--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260811.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>129,898,282</t>
+          <t>158,111,698</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>158,111,698</t>
+          <t>129,898,282</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
